--- a/in/evd_sdb_sim_parameters.xlsx
+++ b/in/evd_sdb_sim_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fchec\Desktop\evd\sim_ifrc\in\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fchec\Desktop\sdb_simulation_2026\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9060211-08EA-448B-A81C-B7907DF47F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF6C75B-825F-466B-A447-1FA84F618DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>parameter</t>
   </si>
@@ -39,25 +39,10 @@
     <t>notes</t>
   </si>
   <si>
-    <t>R0_I</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>R0_D</t>
-  </si>
-  <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>incubation_period</t>
-  </si>
-  <si>
-    <t>infectious_period</t>
-  </si>
-  <si>
-    <t>burial_period</t>
   </si>
   <si>
     <t>cfr</t>
@@ -134,9 +119,6 @@
     <t>assumed based on health zone-specific R values in Checchi et al. (https://researchonline.lshtm.ac.uk/id/eprint/4678756/)</t>
   </si>
   <si>
-    <t>Varied in simulations. R0 = R0_I + R0_D</t>
-  </si>
-  <si>
     <t>Table 5, van Kerkhove et al. (https://www.nature.com/articles/sdata201519/tables/6 )</t>
   </si>
   <si>
@@ -195,6 +177,27 @@
   </si>
   <si>
     <t>Preferably go up to 10,000.</t>
+  </si>
+  <si>
+    <t>T_E</t>
+  </si>
+  <si>
+    <t>T_I</t>
+  </si>
+  <si>
+    <t>T_B</t>
+  </si>
+  <si>
+    <t>Rn_I</t>
+  </si>
+  <si>
+    <t>Rn_D</t>
+  </si>
+  <si>
+    <t>Varied in simulations. Rn = Rn_I + cfr*Rn_D</t>
+  </si>
+  <si>
+    <t>case-fatality ratio</t>
   </si>
 </sst>
 </file>
@@ -245,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -253,22 +256,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,9 +578,9 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="69.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -564,206 +588,227 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="6">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="57" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B10" s="6">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="B11" s="6">
+        <v>90</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B12" s="6">
+        <v>1000</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="57" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="E12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6">
+        <v>211121</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4">
-        <v>90</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4">
-        <v>211121</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
